--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר אופיר – בדמייך חיי</v>
+        <v>מניפסט גם זו לטובה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%91%d7%93%d7%9e%d7%99%d7%99%d7%9a-%d7%97%d7%99%d7%99/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a0%d7%99%d7%a4%d7%a1%d7%98-%d7%92%d7%9d-%d7%96%d7%95-%d7%9c%d7%98%d7%95%d7%91%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-02</v>
+        <v>2026-04-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר בדמייך חיי בביצועה של תמר אופיר, המבוסס על הפסוקים “ואעבור עלייך…” מתוך ספר יחזקאל (שנכנסו גם לנוסח ההגדה), הוא דוגמה יפה לשילוב בין טקסט מקראי טעון לבין פרשנות מוזיקלית עכשווית, רגשית ואינטימית. המילים מהוות ביטוי עוצמתי לקידוש החיים מתוך</v>
+        <v>השיר "גם זו לטובה" של סהר שרה מוסרי (מתוך הפרויקט “מניפסט”) הוא שיר פופ קצבי שמבצע מהלך מעניין: הוא לוקח מציאות יומיומית עמוסת חרדה, תסכול ולחץ, ומנסה להפוך אותה למנטרה של חשיבה חיובית. הכותבת משתמשת ב“גם זו לטובה” כטכניקה מנטלית. המשפט</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר אופיר – בדמייך חיי</v>
+        <v>מניפסט גם זו לטובה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מניפסט גם זו לטובה</v>
+        <v>מניפסט – גם זו לטובה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-04</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מניפסט גם זו לטובה</v>
+        <v>מניפסט – גם זו לטובה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מניפסט – גם זו לטובה</v>
+        <v>חנן בן ארי ופאר טסי – הלוואי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a0%d7%99%d7%a4%d7%a1%d7%98-%d7%92%d7%9d-%d7%96%d7%95-%d7%9c%d7%98%d7%95%d7%91%d7%94/</v>
+        <v>https://yosmusic.com/%d7%97%d7%a0%d7%9f-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%95%d7%a4%d7%90%d7%a8-%d7%98%d7%a1%d7%99-%d7%94%d7%9c%d7%95%d7%95%d7%90%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-04</v>
+        <v>2026-04-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "גם זו לטובה" של סהר שרה מוסרי (מתוך הפרויקט “מניפסט”) הוא שיר פופ קצבי שמבצע מהלך מעניין: הוא לוקח מציאות יומיומית עמוסת חרדה, תסכול ולחץ, ומנסה להפוך אותה למנטרה של חשיבה חיובית. הכותבת משתמשת ב“גם זו לטובה” כטכניקה מנטלית. המשפט</v>
+        <v>השיר ששרים בדואט חנן בן ארי ופאר טסי הנבנה כמענה רגשי קולקטיבי למציאות של משבר, ובמיוחד על רקע תקופות מתוחות כמו מלחמה. המילה “הלוואי” שחוזרת כמעט באובססיביות אינה עמדה אלא משאלה אקראית. השיר לא מתיימר לפתור אלא לבטא כמיהה פשוטה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מניפסט – גם זו לטובה</v>
+        <v>חנן בן ארי ופאר טסי – הלוואי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אבנר טואג – מי אני מה אני מה אני עושה פה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a0%d7%a8-%d7%98%d7%95%d7%90%d7%92-%d7%9e%d7%99-%d7%90%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%a2%d7%95%d7%a9%d7%94-%d7%a4%d7%94/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>אבנר טואג מצליח לקחת שאלה פילוסופית כמעט קלאסית – זהות ומשמעות ולתרגם אותה לחוויה מוזיקלית עכשווית, אישית ונגישה. "מי אני מה אני מה אני עושה פה” – זו אינה רק שאלה אקראית אלא הצפה, בלבול, ניסיון לאחוז במשהו יציב השיר</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אבנר טואג – מי אני מה אני מה אני עושה פה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חנן בן ארי ופאר טסי – הלוואי</v>
+        <v>ילד – חבלמאוד (שאנילאיכולהיותאישה)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%97%d7%a0%d7%9f-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%95%d7%a4%d7%90%d7%a8-%d7%98%d7%a1%d7%99-%d7%94%d7%9c%d7%95%d7%95%d7%90%d7%99/</v>
+        <v>https://yosmusic.com/%d7%99%d7%9c%d7%93-%d7%97%d7%91%d7%9c%d7%9e%d7%90%d7%95%d7%93-%d7%a9%d7%90%d7%a0%d7%99%d7%9c%d7%90%d7%99%d7%9b%d7%95%d7%9c%d7%94%d7%99%d7%95%d7%aa%d7%90%d7%99%d7%a9%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר ששרים בדואט חנן בן ארי ופאר טסי הנבנה כמענה רגשי קולקטיבי למציאות של משבר, ובמיוחד על רקע תקופות מתוחות כמו מלחמה. המילה “הלוואי” שחוזרת כמעט באובססיביות אינה עמדה אלא משאלה אקראית. השיר לא מתיימר לפתור אלא לבטא כמיהה פשוטה</v>
+        <v>השיר "חבל מאוד (שאני לא יכול להיות אישה)" של עומר יפת (והרכב "ילד") הוא שיר רוקנרולי מהיר, כמעט כאוטי, שמשתמש בהומור, חזרתיות והגזמה כדי לפרק ולהרכיב מחדש תפיסות של מגדר, זהות ודימוי עצמי. הקצב המהיר והחזרות המרובות יוצרים תחושת אובססיה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חנן בן ארי ופאר טסי – הלוואי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אבנר טואג – מי אני מה אני מה אני עושה פה</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a0%d7%a8-%d7%98%d7%95%d7%90%d7%92-%d7%9e%d7%99-%d7%90%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%a2%d7%95%d7%a9%d7%94-%d7%a4%d7%94/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>אבנר טואג מצליח לקחת שאלה פילוסופית כמעט קלאסית – זהות ומשמעות ולתרגם אותה לחוויה מוזיקלית עכשווית, אישית ונגישה. "מי אני מה אני מה אני עושה פה” – זו אינה רק שאלה אקראית אלא הצפה, בלבול, ניסיון לאחוז במשהו יציב השיר</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אבנר טואג – מי אני מה אני מה אני עושה פה</v>
+        <v>ילד – חבלמאוד (שאנילאיכולהיותאישה)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ילד – חבלמאוד (שאנילאיכולהיותאישה)</v>
+        <v>נסרין קדרי – יהלום מעבדה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%9c%d7%93-%d7%97%d7%91%d7%9c%d7%9e%d7%90%d7%95%d7%93-%d7%a9%d7%90%d7%a0%d7%99%d7%9c%d7%90%d7%99%d7%9b%d7%95%d7%9c%d7%94%d7%99%d7%95%d7%aa%d7%90%d7%99%d7%a9%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%a1%d7%a8%d7%99%d7%9f-%d7%a7%d7%93%d7%a8%d7%99-%d7%99%d7%94%d7%9c%d7%95%d7%9d-%d7%9e%d7%a2%d7%91%d7%93%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-06</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "חבל מאוד (שאני לא יכול להיות אישה)" של עומר יפת (והרכב "ילד") הוא שיר רוקנרולי מהיר, כמעט כאוטי, שמשתמש בהומור, חזרתיות והגזמה כדי לפרק ולהרכיב מחדש תפיסות של מגדר, זהות ודימוי עצמי. הקצב המהיר והחזרות המרובות יוצרים תחושת אובססיה</v>
+        <v>השיר "יהלום מעבדה" מציג את הפרסונה העכשווית של נסרין קדר, שיר חפלה שמאמץ במודע אסתטיקה "נמוכה", פרובוקטיבית ומוגזמת, כדי לייצר גם בידור וגם ביקורת חברתית גם אם לא תמיד ברור עד כמה הביקורת מכוונת. השיר מפרק את הפנטזיה של זיווג</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ילד – חבלמאוד (שאנילאיכולהיותאישה)</v>
+        <v>נסרין קדרי – יהלום מעבדה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נסרין קדרי – יהלום מעבדה</v>
+        <v>ישי ריבו – לא לחינם</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%a1%d7%a8%d7%99%d7%9f-%d7%a7%d7%93%d7%a8%d7%99-%d7%99%d7%94%d7%9c%d7%95%d7%9d-%d7%9e%d7%a2%d7%91%d7%93%d7%94/</v>
+        <v>https://yosmusic.com/%d7%99%d7%a9%d7%99-%d7%a8%d7%99%d7%91%d7%95-%d7%9c%d7%90-%d7%9c%d7%97%d7%99%d7%a0%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "יהלום מעבדה" מציג את הפרסונה העכשווית של נסרין קדר, שיר חפלה שמאמץ במודע אסתטיקה "נמוכה", פרובוקטיבית ומוגזמת, כדי לייצר גם בידור וגם ביקורת חברתית גם אם לא תמיד ברור עד כמה הביקורת מכוונת. השיר מפרק את הפנטזיה של זיווג</v>
+        <v>ישי ריבו שר שיר מורכב שמשלב את סגנונו האמוני  עם מבנה מודרני ומגוון, הכולל גם פזמון מלודי ובתים בסגנון ראפ. השיר עוסק בכמה שכבות מרכזיות: אדם מול יצרו – "עושה היצר זבלו אוצר / גאון הדור בשיווק מוצר" הריבוי בין</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נסרין קדרי – יהלום מעבדה</v>
+        <v>ישי ריבו – לא לחינם</v>
       </c>
     </row>
   </sheetData>
